--- a/source/INVOICE.xlsx
+++ b/source/INVOICE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\ADMISSION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F1B7E6-8B59-418F-9DCC-CB423CA67BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A416FF2D-AB63-4108-986C-8558ABD615E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1146,7 +1146,7 @@
         <v>6000</v>
       </c>
       <c r="H12" s="8">
-        <v>19560</v>
+        <v>19320</v>
       </c>
       <c r="I12" s="10">
         <v>16190</v>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="Q12" s="17">
         <f t="shared" si="0"/>
-        <v>120750</v>
+        <v>120510</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1200,7 +1200,7 @@
         <v>6000</v>
       </c>
       <c r="H13" s="8">
-        <v>19560</v>
+        <v>19500</v>
       </c>
       <c r="I13" s="10">
         <v>14330</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Q13" s="17">
         <f t="shared" si="0"/>
-        <v>118890</v>
+        <v>118830</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1254,7 +1254,7 @@
         <v>6000</v>
       </c>
       <c r="H14" s="8">
-        <v>22580</v>
+        <v>22400</v>
       </c>
       <c r="I14" s="10">
         <v>14330</v>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="Q14" s="17">
         <f t="shared" si="0"/>
-        <v>121910</v>
+        <v>121730</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/source/INVOICE.xlsx
+++ b/source/INVOICE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A416FF2D-AB63-4108-986C-8558ABD615E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75505F5C-EDCB-4D0D-BB41-EDB85E88C68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -876,7 +876,7 @@
         <v>5000</v>
       </c>
       <c r="H7" s="8">
-        <v>25550</v>
+        <v>25490</v>
       </c>
       <c r="I7" s="10">
         <v>11330</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="Q7" s="17">
         <f t="shared" si="0"/>
-        <v>115380</v>
+        <v>115320</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -930,7 +930,7 @@
         <v>5000</v>
       </c>
       <c r="H8" s="8">
-        <v>25730</v>
+        <v>25670</v>
       </c>
       <c r="I8" s="10">
         <v>11330</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="Q8" s="17">
         <f t="shared" si="0"/>
-        <v>115560</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -984,7 +984,7 @@
         <v>5000</v>
       </c>
       <c r="H9" s="8">
-        <v>26890</v>
+        <v>26830</v>
       </c>
       <c r="I9" s="10">
         <v>13230</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Q9" s="17">
         <f t="shared" si="0"/>
-        <v>118620</v>
+        <v>118560</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1038,7 +1038,7 @@
         <v>5000</v>
       </c>
       <c r="H10" s="8">
-        <v>26910</v>
+        <v>26850</v>
       </c>
       <c r="I10" s="10">
         <v>13230</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Q10" s="17">
         <f t="shared" si="0"/>
-        <v>118640</v>
+        <v>118580</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
@@ -1092,7 +1092,7 @@
         <v>5000</v>
       </c>
       <c r="H11" s="8">
-        <v>28850</v>
+        <v>28790</v>
       </c>
       <c r="I11" s="10">
         <v>13230</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Q11" s="17">
         <f t="shared" si="0"/>
-        <v>120580</v>
+        <v>120520</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/source/INVOICE.xlsx
+++ b/source/INVOICE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75505F5C-EDCB-4D0D-BB41-EDB85E88C68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85691A89-0702-4455-BD6E-63C07611C216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="8">
-        <v>24450</v>
+        <v>24930</v>
       </c>
       <c r="I6" s="10">
         <v>10730</v>
@@ -850,7 +850,7 @@
       </c>
       <c r="Q6" s="17">
         <f t="shared" si="0"/>
-        <v>105180</v>
+        <v>105660</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -876,7 +876,7 @@
         <v>5000</v>
       </c>
       <c r="H7" s="8">
-        <v>25490</v>
+        <v>25970</v>
       </c>
       <c r="I7" s="10">
         <v>11330</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="Q7" s="17">
         <f t="shared" si="0"/>
-        <v>115320</v>
+        <v>115800</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -930,7 +930,7 @@
         <v>5000</v>
       </c>
       <c r="H8" s="8">
-        <v>25670</v>
+        <v>26150</v>
       </c>
       <c r="I8" s="10">
         <v>11330</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="Q8" s="17">
         <f t="shared" si="0"/>
-        <v>115500</v>
+        <v>115980</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -984,7 +984,7 @@
         <v>5000</v>
       </c>
       <c r="H9" s="8">
-        <v>26830</v>
+        <v>27310</v>
       </c>
       <c r="I9" s="10">
         <v>13230</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Q9" s="17">
         <f t="shared" si="0"/>
-        <v>118560</v>
+        <v>119040</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1038,7 +1038,7 @@
         <v>5000</v>
       </c>
       <c r="H10" s="8">
-        <v>26850</v>
+        <v>27330</v>
       </c>
       <c r="I10" s="10">
         <v>13230</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Q10" s="17">
         <f t="shared" si="0"/>
-        <v>118580</v>
+        <v>119060</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
